--- a/附录1：测试用例清单.xlsx
+++ b/附录1：测试用例清单.xlsx
@@ -942,50 +942,6 @@
     </graphicFrame>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>9525</colOff>
-      <row>0</row>
-      <rowOff>104775</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>95250</colOff>
-      <row>2</row>
-      <rowOff>57150</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2056" name="Picture 4"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="152400" y="104775"/>
-          <a:ext cx="2828925" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -2453,7 +2409,7 @@
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t>归一化下界=0.0 上界=1.0；反解下界=-180.0°；返回类型 lo=NoneType hi=NoneType</t>
+          <t>归一化下界=0.0 上界=1.0；反解下界=-180.0°；返回类型 lo=ndarray hi=ndarray</t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
@@ -3485,12 +3441,12 @@
       </c>
       <c r="K18" s="42" t="inlineStr">
         <is>
-          <t>回合结束后，按模块自身 FK 计算 self.target 处夹爪中心距目标 0.11000 m（Muli=0.11000，阈值 0.05 m）</t>
+          <t>回合结束后，按模块自身 FK 计算 self.target 处夹爪中心距目标 0.04850 m（Muli=0.04850，阈值 0.05 m）</t>
         </is>
       </c>
       <c r="L18" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M18" s="42" t="inlineStr">
@@ -4709,12 +4665,12 @@
       </c>
       <c r="K36" s="42" t="inlineStr">
         <is>
-          <t>bdb=40.0000° A5=-90.0 时 strategies=['A2Up', 'A3Up', 'A4Up']（不含 A1 方向）</t>
+          <t>bdb=40.0000° A5=-90.0 时 strategies=['A1Right', 'A2Up', 'A3Up', 'A4Up']（不含 A1 方向）</t>
         </is>
       </c>
       <c r="L36" s="42" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="M36" s="42" t="inlineStr">
@@ -4777,12 +4733,12 @@
       </c>
       <c r="K37" s="42" t="inlineStr">
         <is>
-          <t>DFL 覆盖后 A4=0.0 A5=-30.0 A6=45.0</t>
+          <t>TypeError: MyCustomAlgorithm.__init__() got an unexpected keyword argument 'A4'</t>
         </is>
       </c>
       <c r="L37" s="42" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="M37" s="42" t="inlineStr">
@@ -4845,7 +4801,7 @@
       </c>
       <c r="K38" s="42" t="inlineStr">
         <is>
-          <t>超程目标处理正常，返回 NoneType</t>
+          <t>超程目标处理正常，返回 ndarray</t>
         </is>
       </c>
       <c r="L38" s="42" t="inlineStr">
@@ -4981,12 +4937,12 @@
       </c>
       <c r="K40" s="42" t="inlineStr">
         <is>
-          <t>返回 None，env.step 中 np.clip 抛出 TypeError: '&gt;=' not supported between instances of 'NoneType' and 'int'</t>
+          <t>未触发弃权路径，正常返回动作</t>
         </is>
       </c>
       <c r="L40" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M40" s="42" t="inlineStr">
@@ -5185,7 +5141,7 @@
       </c>
       <c r="K43" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终夹爪-目标距离 0.18612 m（阈值 0.05），得分 9.25</t>
+          <t>100 步结束，最终夹爪-目标距离 0.12462 m（阈值 0.05），得分 50.25</t>
         </is>
       </c>
       <c r="L43" s="42" t="inlineStr">
@@ -5253,7 +5209,7 @@
       </c>
       <c r="K44" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终距离 0.18612 m，得分 9.25</t>
+          <t>100 步结束，最终距离 0.12462 m，得分 50.25</t>
         </is>
       </c>
       <c r="L44" s="42" t="inlineStr">
@@ -5321,7 +5277,7 @@
       </c>
       <c r="K45" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终距离 0.18612 m，得分 9.25</t>
+          <t>100 步结束，最终距离 0.12462 m，得分 50.25</t>
         </is>
       </c>
       <c r="L45" s="42" t="inlineStr">
@@ -5389,7 +5345,7 @@
       </c>
       <c r="K46" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终距离 0.18612 m，得分 9.25</t>
+          <t>100 步结束，最终距离 0.12462 m，得分 50.25</t>
         </is>
       </c>
       <c r="L46" s="42" t="inlineStr">
@@ -5457,7 +5413,7 @@
       </c>
       <c r="K47" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终距离 0.18612 m，得分 9.25</t>
+          <t>100 步结束，最终距离 0.12462 m，得分 50.25</t>
         </is>
       </c>
       <c r="L47" s="42" t="inlineStr">
@@ -5525,7 +5481,7 @@
       </c>
       <c r="K48" s="42" t="inlineStr">
         <is>
-          <t>低年级组：100 步结束，最终距离 0.18612 m，得分 9.25</t>
+          <t>低年级组：100 步结束，最终距离 0.12462 m，得分 50.25</t>
         </is>
       </c>
       <c r="L48" s="42" t="inlineStr">
@@ -5593,7 +5549,7 @@
       </c>
       <c r="K49" s="42" t="inlineStr">
         <is>
-          <t>10 个随机回合成功率 0%，最终距离均值 0.18612 m（要求 ≥80%）</t>
+          <t>10 个随机回合成功率 0%，最终距离均值 0.12462 m（要求 ≥80%）</t>
         </is>
       </c>
       <c r="L49" s="42" t="inlineStr">
